--- a/output.xlsx
+++ b/output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,127 +424,67 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>order_number</t>
+          <t>invoice_date</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>order_date</t>
+          <t>vendor_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>sold_to</t>
+          <t>customer_name</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>ship_to</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>tax_amount</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>contact_person</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>payment_method</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>shipping_method</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>shipping_charges</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>products</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>currency</t>
+          <t>total_amount</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2000000056</t>
+          <t>901840429</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2000000117</t>
+          <t>18.03.2020</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2019-02-26</t>
+          <t>ALFANAR COMPANY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>نايفاس يبأنب ةيواعم</t>
+          <t>SABCO ALMABANI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نايفاس يبأنب ذيواعم</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>يريطمل | ردب وبا</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0564039119</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>مات سال ا دن عفدل</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>20</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>[{'sku': '5055268027141', 'name': 'Alford Duvet', 'description': 'دروفل أريرس شرفم مقط', 'quantity': 1, 'unit_price': 223.3, 'tax': 11.17, 'subtotal': 223.3}, {'sku': None, 'name': 'BLE Double', 'description': '200x20', 'quantity': None, 'unit_price': None, 'tax': None, 'subtotal': None}]</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>16473.63</v>
+      </c>
+      <c r="G2" t="n">
+        <v>345946</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output.xlsx
+++ b/output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,15 +439,35 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>customer_number</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>purchase_order_number</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>vat_registration_number</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subtotal</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>tax_amount</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>total_amount</t>
         </is>
@@ -476,14 +496,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>7049</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CEO0-F0R0-00076</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>300050206400003</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
+        <v>329472.67</v>
+      </c>
+      <c r="J2" t="n">
         <v>16473.63</v>
       </c>
-      <c r="G2" t="n">
-        <v>345946</v>
+      <c r="K2" t="n">
+        <v>345946.3</v>
       </c>
     </row>
   </sheetData>
